--- a/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91985\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91985\Desktop\Asgns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CD47F7-23AC-4D56-A7ED-8F2FF86FE0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29566D7-84F5-42B4-BA69-353EF67F6AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="95">
   <si>
     <t>Skill</t>
   </si>
@@ -340,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,6 +362,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -535,6 +547,24 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -561,29 +591,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57EFDF7-9EDE-4E32-9B50-93240323B319}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.109375" customWidth="1"/>
@@ -928,22 +941,22 @@
     <col min="5" max="5" width="30.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="18"/>
+      <c r="E1" s="28"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="20"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -953,14 +966,14 @@
       <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -971,13 +984,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="4"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" s="27"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E3" s="10"/>
+      <c r="F3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -988,14 +1001,12 @@
         <v>5</v>
       </c>
       <c r="D4" s="4"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-    </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E4" s="10"/>
+      <c r="F4" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1006,12 +1017,12 @@
         <v>8</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E5" s="10"/>
+      <c r="F5" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -1022,12 +1033,12 @@
         <v>9</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E6" s="10"/>
+      <c r="F6" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1038,13 +1049,12 @@
         <v>12</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H7" s="28"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E7" s="10"/>
+      <c r="F7" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1055,12 +1065,12 @@
         <v>13</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E8" s="10"/>
+      <c r="F8" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -1071,10 +1081,12 @@
         <v>16</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E9" s="10"/>
+      <c r="F9" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -1085,34 +1097,40 @@
         <v>17</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="14"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="22"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D12" s="22"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -1123,10 +1141,12 @@
         <v>21</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E13" s="10"/>
+      <c r="F13" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -1137,10 +1157,12 @@
         <v>22</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E14" s="10"/>
+      <c r="F14" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1151,10 +1173,12 @@
         <v>25</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E15" s="10"/>
+      <c r="F15" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
@@ -1165,10 +1189,12 @@
         <v>28</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="8"/>
+      <c r="F16" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
@@ -1181,10 +1207,12 @@
         <v>30</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
@@ -1197,10 +1225,12 @@
         <v>32</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="8"/>
+      <c r="F18" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
@@ -1215,10 +1245,12 @@
       <c r="D19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="8"/>
+      <c r="F19" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -1233,10 +1265,12 @@
       <c r="D20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="8"/>
+      <c r="F20" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
@@ -1247,10 +1281,12 @@
       <c r="D21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="8"/>
+      <c r="F21" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -1261,10 +1297,12 @@
       <c r="D22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="8"/>
+      <c r="F22" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -1275,10 +1313,12 @@
       <c r="D23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="8"/>
+      <c r="F23" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
@@ -1289,10 +1329,12 @@
       <c r="D24" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="8"/>
+      <c r="F24" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
@@ -1301,16 +1343,18 @@
       <c r="B25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="8"/>
+      <c r="F25" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -1319,12 +1363,14 @@
       <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="17" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="4"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="8"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
@@ -1333,12 +1379,14 @@
       <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="18" t="s">
         <v>53</v>
       </c>
       <c r="D27" s="4"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="8"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
@@ -1347,12 +1395,14 @@
       <c r="B28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="18" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="8"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
@@ -1361,12 +1411,14 @@
       <c r="B29" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="18" t="s">
         <v>55</v>
       </c>
       <c r="D29" s="4"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="8"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
@@ -1379,36 +1431,42 @@
         <v>57</v>
       </c>
       <c r="D30" s="4"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="8"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="8"/>
+      <c r="F31" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="24" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="8"/>
+      <c r="F32" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
@@ -1423,10 +1481,10 @@
       <c r="D33" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="26" t="s">
+      <c r="E33" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="14" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1443,10 +1501,10 @@
       <c r="D34" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="26" t="s">
+      <c r="E34" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="14" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1463,10 +1521,10 @@
       <c r="D35" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" s="26" t="s">
+      <c r="E35" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1481,8 +1539,10 @@
         <v>65</v>
       </c>
       <c r="D36" s="4"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="8"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
@@ -1495,8 +1555,10 @@
         <v>65</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="8"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
@@ -1511,10 +1573,12 @@
       <c r="D38" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="8"/>
+      <c r="E38" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -1529,10 +1593,12 @@
       <c r="D39" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" s="8"/>
+      <c r="E39" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
@@ -1547,7 +1613,7 @@
       <c r="D40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="10" t="s">
         <v>65</v>
       </c>
       <c r="F40" s="8"/>
@@ -1565,7 +1631,7 @@
       <c r="D41" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="10" t="s">
         <v>65</v>
       </c>
       <c r="F41" s="8"/>
@@ -1583,7 +1649,7 @@
       <c r="D42" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="10" t="s">
         <v>65</v>
       </c>
       <c r="F42" s="8"/>
@@ -1599,7 +1665,7 @@
         <v>65</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="20"/>
+      <c r="E43" s="10"/>
       <c r="F43" s="8"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1613,7 +1679,7 @@
         <v>65</v>
       </c>
       <c r="D44" s="4"/>
-      <c r="E44" s="20"/>
+      <c r="E44" s="10"/>
       <c r="F44" s="8"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1627,7 +1693,7 @@
         <v>65</v>
       </c>
       <c r="D45" s="4"/>
-      <c r="E45" s="20"/>
+      <c r="E45" s="10"/>
       <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1641,7 +1707,7 @@
         <v>65</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="20"/>
+      <c r="E46" s="10"/>
       <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1655,7 +1721,7 @@
         <v>65</v>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="20"/>
+      <c r="E47" s="10"/>
       <c r="F47" s="8"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -1669,7 +1735,7 @@
         <v>65</v>
       </c>
       <c r="D48" s="8"/>
-      <c r="E48" s="25"/>
+      <c r="E48" s="13"/>
       <c r="F48" s="8"/>
     </row>
   </sheetData>

--- a/DN - Java FSE Mandatory hands-on detail.xlsx
+++ b/DN - Java FSE Mandatory hands-on detail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91985\Desktop\Asgns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29566D7-84F5-42B4-BA69-353EF67F6AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C20D3A6-BF91-4D93-A6A2-4526A155932D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E078EC40-2268-4F4F-B14B-9403122955B8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="95">
   <si>
     <t>Skill</t>
   </si>
@@ -340,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,13 +367,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,8 +557,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -597,6 +589,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -942,21 +936,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="28"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
+      <c r="A2" s="18"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1103,29 +1097,29 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="29"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="24"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="30"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="14" t="s">
         <v>94</v>
       </c>
@@ -1343,7 +1337,7 @@
       <c r="B25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="30" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="4" t="s">
@@ -1363,7 +1357,7 @@
       <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="30" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="4"/>
@@ -1379,7 +1373,7 @@
       <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="30" t="s">
         <v>53</v>
       </c>
       <c r="D27" s="4"/>
@@ -1395,7 +1389,7 @@
       <c r="B28" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="30" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="4"/>
@@ -1411,7 +1405,7 @@
       <c r="B29" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="30" t="s">
         <v>55</v>
       </c>
       <c r="D29" s="4"/>
@@ -1437,16 +1431,16 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="19" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="11" t="s">
@@ -1457,10 +1451,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="20"/>
       <c r="E32" s="12" t="s">
         <v>62</v>
       </c>
@@ -1616,7 +1610,9 @@
       <c r="E40" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="8"/>
+      <c r="F40" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
@@ -1634,7 +1630,9 @@
       <c r="E41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F41" s="8"/>
+      <c r="F41" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
@@ -1652,7 +1650,9 @@
       <c r="E42" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="8"/>
+      <c r="F42" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
@@ -1666,7 +1666,9 @@
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="10"/>
-      <c r="F43" s="8"/>
+      <c r="F43" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
@@ -1680,7 +1682,9 @@
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="10"/>
-      <c r="F44" s="8"/>
+      <c r="F44" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
@@ -1694,7 +1698,9 @@
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="10"/>
-      <c r="F45" s="8"/>
+      <c r="F45" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
@@ -1708,7 +1714,9 @@
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="10"/>
-      <c r="F46" s="8"/>
+      <c r="F46" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
@@ -1722,7 +1730,9 @@
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="10"/>
-      <c r="F47" s="8"/>
+      <c r="F47" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
@@ -1736,7 +1746,9 @@
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="13"/>
-      <c r="F48" s="8"/>
+      <c r="F48" s="29" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1757,15 +1769,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
@@ -1774,6 +1777,15 @@
     <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2037,14 +2049,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B84191-BBE7-412A-A5F6-7B8D27AECA6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -2058,6 +2062,14 @@
     <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F0F638-0648-46BA-B1DF-3E4F6ADB00E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
